--- a/jogos_2025-10-04.xlsx
+++ b/jogos_2025-10-04.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Albirex Niigata</t>
+          <t>JEF United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fagiano Okayama</t>
+          <t>V-Varen Nagasaki</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gwangju</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Consadole Sapporo</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Montedio Yamagata</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JEF United</t>
+          <t>Albirex Niigata</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>V-Varen Nagasaki</t>
+          <t>Fagiano Okayama</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gwangju</t>
+          <t>Consadole Sapporo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Montedio Yamagata</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Japan J2 League</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vegalta Sendai</t>
+          <t>Avispa Fukuoka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Omiya Ardija</t>
+          <t>Yokohama</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Japan J2 League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avispa Fukuoka</t>
+          <t>Vegalta Sendai</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yokohama</t>
+          <t>Omiya Ardija</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Incheon United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Incheon United</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Urawa Reds</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Vissel Kobe</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Urawa Reds</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vissel Kobe</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Japan J1 League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Kyoto Sanga</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Kawasaki Frontale</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Akron</t>
+          <t>Lusitania Lourosa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Farense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lusitania Lourosa</t>
+          <t>Oleksandria</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Farense</t>
+          <t>Karpaty</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,22 +4632,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Japan J1 League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kyoto Sanga</t>
+          <t>Akron</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kawasaki Frontale</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oleksandria</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karpaty</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pendikspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Adana Demirspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Pendikspor</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Adana Demirspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ufa</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hertha BSC</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Chiangrai United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Rayong</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Hertha BSC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="M43" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N43" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chiangrai United</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rayong</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Ufa</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Borneo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Viktoria Köln</t>
+          <t>Jahn Regensburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Waldhof Mannheim</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Betis II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Viktoria Köln</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Suduroy</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Vålerenga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Tromsø</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Buxoro</t>
+          <t>Reims</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,22 +10695,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vålerenga</t>
+          <t>Real Betis II</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tromsø</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Persita</t>
+          <t>Real Oviedo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10856,65 +10856,65 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Oviedo</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Suduroy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Borneo</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Jahn Regensburg</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Waldhof Mannheim</t>
+          <t>Persita</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11501,65 +11501,65 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         </is>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Reims</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Buxoro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Rubin Kazan</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.3</v>
+        <v>2.05</v>
       </c>
       <c r="M91" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="N91" t="n">
-        <v>10</v>
+        <v>3.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rubin Kazan</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.05</v>
+        <v>1.3</v>
       </c>
       <c r="M92" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="N92" t="n">
-        <v>3.6</v>
+        <v>10</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ayutthaya United</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ayutthaya United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Obolon-Brovar</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Veres Rivne</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Obolon-Brovar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Teplice</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Elfsborg</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.65</v>
+        <v>5</v>
       </c>
       <c r="M106" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N106" t="n">
-        <v>4.7</v>
+        <v>1.58</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kuala Lumpur</t>
+          <t>Elfsborg</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Halmstad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Teplice</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Pardubice</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FS Jelgava</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Halmstad</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="M114" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N114" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Avellino</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N116" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,16 +15543,16 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AB117" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Kuala Lumpur</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Connah's Quay</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Llanelli Town</t>
+          <t>FS Jelgava</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Van BB</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Connah's Quay</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Van BB</t>
+          <t>Llanelli Town</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Avellino</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.55</v>
+        <v>2.65</v>
       </c>
       <c r="M130" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="N130" t="n">
-        <v>5.6</v>
+        <v>2.5</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,16 +17220,16 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA130" t="n">
-        <v>2.22</v>
+        <v>2.39</v>
       </c>
       <c r="AB130" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="AC130" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="M131" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="N131" t="n">
-        <v>2.5</v>
+        <v>5.6</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,16 +17349,16 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z131" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA131" t="n">
-        <v>2.39</v>
+        <v>2.22</v>
       </c>
       <c r="AB131" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="AC131" t="n">
         <v>0</v>
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>KA</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Vestri</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,22 +17661,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Alingsås</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Marbella FC</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,22 +17790,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Eyüpspor</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,22 +17919,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Mariehamn</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18084,13 +18084,13 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N137" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O137" t="n">
         <v>0</v>
@@ -18123,10 +18123,10 @@
         <v>0</v>
       </c>
       <c r="Y137" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z137" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA137" t="n">
         <v>0</v>
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>KA</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vestri</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,7 +18306,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -18316,12 +18316,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Airdrieonians</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -18574,12 +18574,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Dundee United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18729,13 +18729,13 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N142" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O142" t="n">
         <v>0</v>
@@ -18768,10 +18768,10 @@
         <v>0</v>
       </c>
       <c r="Y142" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z142" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA142" t="n">
         <v>0</v>
@@ -18822,7 +18822,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -18832,12 +18832,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kilmarnock</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Eyüpspor</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19026,10 +19026,10 @@
         <v>0</v>
       </c>
       <c r="Y144" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z144" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA144" t="n">
         <v>0</v>
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Afturelding</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19209,7 +19209,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N147" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19413,16 +19413,16 @@
         <v>0</v>
       </c>
       <c r="Y147" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z147" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB147" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Kilmarnock</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19725,7 +19725,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vyškov</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19854,22 +19854,22 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,22 +20241,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20370,22 +20370,22 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20628,22 +20628,22 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Sandefjord</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bryne</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,22 +20757,22 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Airdrieonians</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -21015,22 +21015,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Alingsås</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21402,22 +21402,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21531,22 +21531,22 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21660,22 +21660,22 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>ÍA</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Dundee United</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21825,13 +21825,13 @@
         </is>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N166" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O166" t="n">
         <v>0</v>
@@ -21864,10 +21864,10 @@
         <v>0</v>
       </c>
       <c r="Y166" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA166" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z167" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22176,22 +22176,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22305,22 +22305,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Watford</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,22 +22434,22 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22563,22 +22563,22 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22950,22 +22950,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Enosis</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23337,22 +23337,22 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Sandefjord</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Bryne</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Northampton Town</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23724,22 +23724,22 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Afturelding</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23853,22 +23853,22 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Enosis</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>KAA Gent II</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24369,7 +24369,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M186" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24444,16 +24444,16 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z186" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA186" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB186" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AC186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Watford</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Marbella FC</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24627,22 +24627,22 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Mariehamn</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24885,22 +24885,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -25014,22 +25014,22 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,22 +25143,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Northampton Town</t>
+          <t>ÍA</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25272,7 +25272,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>KAA Gent II</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Vyškov</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26304,7 +26304,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>AD Alcorcón</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Valencia CF</t>
+          <t>Atlético Sanluqueño CF</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CP Cacereño</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,22 +26562,22 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>CD Eldense</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26691,22 +26691,22 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>AD Alcorcón</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Atlético Sanluqueño CF</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>CP Cacereño</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26949,7 +26949,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -26959,12 +26959,12 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>CD Eldense</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Valencia CF</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Akhmat Grozny</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27243,13 +27243,13 @@
         </is>
       </c>
       <c r="L208" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N208" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="O208" t="n">
         <v>0</v>
@@ -27282,10 +27282,10 @@
         <v>0</v>
       </c>
       <c r="Y208" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z208" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA208" t="n">
         <v>0</v>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>CD Nacional</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Moreirense FC</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M209" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N209" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27411,10 +27411,10 @@
         <v>0</v>
       </c>
       <c r="Y209" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z209" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA209" t="n">
         <v>0</v>
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27630,13 +27630,13 @@
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M211" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O211" t="n">
         <v>0</v>
@@ -27669,10 +27669,10 @@
         <v>0</v>
       </c>
       <c r="Y211" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z211" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA211" t="n">
         <v>0</v>
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Alemannia Aachen</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27759,13 +27759,13 @@
         </is>
       </c>
       <c r="L212" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="M212" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N212" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O212" t="n">
         <v>0</v>
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>CD Nacional</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Moreirense FC</t>
+          <t>Akhmat Grozny</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M213" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N213" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Wattens</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Polessya</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>SK Poltava</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29142,7 +29142,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Metz</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29271,7 +29271,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Metz</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Polessya</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>SK Poltava</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Panserraikos</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Wattens</t>
+          <t>Asteras Tripolis</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z233" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30690,22 +30690,22 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30726,13 +30726,13 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N235" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O235" t="n">
         <v>0</v>
@@ -30765,10 +30765,10 @@
         <v>0</v>
       </c>
       <c r="Y235" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z235" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA235" t="n">
         <v>0</v>
@@ -30819,22 +30819,22 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30855,13 +30855,13 @@
         </is>
       </c>
       <c r="L236" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N236" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O236" t="n">
         <v>0</v>
@@ -30894,10 +30894,10 @@
         <v>0</v>
       </c>
       <c r="Y236" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z236" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA236" t="n">
         <v>0</v>
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Panserraikos</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Asteras Tripolis</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31371,13 +31371,13 @@
         </is>
       </c>
       <c r="L240" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N240" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
         <v>0</v>
@@ -31410,10 +31410,10 @@
         <v>0</v>
       </c>
       <c r="Y240" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z240" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA240" t="n">
         <v>0</v>
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -31861,12 +31861,12 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -31980,7 +31980,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -31990,12 +31990,12 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>OFI</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32184,10 +32184,10 @@
         <v>0</v>
       </c>
       <c r="Y246" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z246" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA246" t="n">
         <v>0</v>
@@ -32238,22 +32238,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32274,13 +32274,13 @@
         </is>
       </c>
       <c r="L247" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N247" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O247" t="n">
         <v>0</v>
@@ -32313,10 +32313,10 @@
         <v>0</v>
       </c>
       <c r="Y247" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z247" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA247" t="n">
         <v>0</v>
@@ -32367,22 +32367,22 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32403,13 +32403,13 @@
         </is>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O248" t="n">
         <v>0</v>
@@ -32442,10 +32442,10 @@
         <v>0</v>
       </c>
       <c r="Y248" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z248" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA248" t="n">
         <v>0</v>
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32754,7 +32754,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -32764,12 +32764,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>OFI</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32829,10 +32829,10 @@
         <v>0</v>
       </c>
       <c r="Y251" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z251" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA251" t="n">
         <v>0</v>
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Komárno</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Tatran Prešov</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -32919,13 +32919,13 @@
         </is>
       </c>
       <c r="L252" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="N252" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
         <v>0</v>
@@ -32958,16 +32958,16 @@
         <v>0</v>
       </c>
       <c r="Y252" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z252" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA252" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB252" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC252" t="n">
         <v>0</v>
@@ -33012,7 +33012,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -33022,12 +33022,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,7 +33141,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -33151,12 +33151,12 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Osijek</t>
+          <t>Keçiörengücü</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33306,13 +33306,13 @@
         </is>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O255" t="n">
         <v>0</v>
@@ -33345,16 +33345,16 @@
         <v>0</v>
       </c>
       <c r="Y255" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z255" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA255" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB255" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC255" t="n">
         <v>0</v>
@@ -33528,22 +33528,22 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Keçiörengücü</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,22 +33657,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Podbrezová</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Spartak Trnava</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33786,7 +33786,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -33796,12 +33796,12 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Zemplín Michalovce</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Trenčín</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,7 +33915,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -33925,12 +33925,12 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Komárno</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Tatran Prešov</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,7 +34044,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -34054,12 +34054,12 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>St. Gallen</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,7 +34173,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -34183,12 +34183,12 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34302,7 +34302,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -34312,12 +34312,12 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>St. Gallen</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Osijek</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -34699,12 +34699,12 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Podbrezová</t>
+          <t>Zemplín Michalovce</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Spartak Trnava</t>
+          <t>Trenčín</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -34818,22 +34818,22 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>07 Vestur</t>
+          <t>Colwyn Bay</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Caernarfon Town</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Zulte-Waregem</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="M268" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z268" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35076,22 +35076,22 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Colwyn Bay</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Caernarfon Town</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35334,22 +35334,22 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>07 Vestur</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Zulte-Waregem</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,22 +35463,22 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Athletic Club Bilbao</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,7 +35850,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -35860,12 +35860,12 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -35886,13 +35886,13 @@
         </is>
       </c>
       <c r="L275" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N275" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
         <v>0</v>
@@ -35931,10 +35931,10 @@
         <v>0</v>
       </c>
       <c r="AA275" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB275" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC275" t="n">
         <v>0</v>
@@ -35979,7 +35979,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -35989,12 +35989,12 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -36015,13 +36015,13 @@
         </is>
       </c>
       <c r="L276" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N276" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
         <v>0</v>
@@ -36054,16 +36054,16 @@
         <v>0</v>
       </c>
       <c r="Y276" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z276" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA276" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB276" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC276" t="n">
         <v>0</v>
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Athletic Club Bilbao</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36144,13 +36144,13 @@
         </is>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="M277" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O277" t="n">
         <v>0</v>
@@ -36189,10 +36189,10 @@
         <v>0</v>
       </c>
       <c r="AA277" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB277" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC277" t="n">
         <v>0</v>
@@ -36247,12 +36247,12 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36624,7 +36624,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -36634,12 +36634,12 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36882,7 +36882,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -36918,13 +36918,13 @@
         </is>
       </c>
       <c r="L283" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M283" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O283" t="n">
         <v>0</v>
@@ -36957,16 +36957,16 @@
         <v>0</v>
       </c>
       <c r="Y283" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z283" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA283" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB283" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC283" t="n">
         <v>0</v>
@@ -37011,7 +37011,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dinamo Moskva</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>Lokomotiv Moskva</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,49 +37176,49 @@
         </is>
       </c>
       <c r="L285" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M285" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N285" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="P285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="n">
+        <v>0</v>
+      </c>
+      <c r="T285" t="n">
+        <v>0</v>
+      </c>
+      <c r="U285" t="n">
+        <v>0</v>
+      </c>
+      <c r="V285" t="n">
+        <v>0</v>
+      </c>
+      <c r="W285" t="n">
+        <v>0</v>
+      </c>
+      <c r="X285" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y285" t="n">
         <v>1.85</v>
       </c>
-      <c r="M285" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N285" t="n">
-        <v>4</v>
-      </c>
-      <c r="O285" t="n">
-        <v>0</v>
-      </c>
-      <c r="P285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q285" t="n">
-        <v>0</v>
-      </c>
-      <c r="R285" t="n">
-        <v>0</v>
-      </c>
-      <c r="S285" t="n">
-        <v>0</v>
-      </c>
-      <c r="T285" t="n">
-        <v>0</v>
-      </c>
-      <c r="U285" t="n">
-        <v>0</v>
-      </c>
-      <c r="V285" t="n">
-        <v>0</v>
-      </c>
-      <c r="W285" t="n">
-        <v>0</v>
-      </c>
-      <c r="X285" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y285" t="n">
-        <v>1.8</v>
-      </c>
       <c r="Z285" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Tractor Sazi</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37434,13 +37434,13 @@
         </is>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O287" t="n">
         <v>0</v>
@@ -37473,10 +37473,10 @@
         <v>0</v>
       </c>
       <c r="Y287" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA287" t="n">
         <v>0</v>
@@ -37527,7 +37527,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -37537,12 +37537,12 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Dinamo Moskva</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Lokomotiv Moskva</t>
+          <t>Tractor Sazi</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37563,13 +37563,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N288" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>0</v>
       </c>
       <c r="Y288" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z288" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA288" t="n">
         <v>0</v>
@@ -37656,22 +37656,22 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,22 +37785,22 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Volos NFC</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37821,13 +37821,13 @@
         </is>
       </c>
       <c r="L290" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M290" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O290" t="n">
         <v>0</v>
@@ -37860,10 +37860,10 @@
         <v>0</v>
       </c>
       <c r="Y290" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z290" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA290" t="n">
         <v>0</v>
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>AEL</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Anorthosis</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,22 +38172,22 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,7 +38301,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -38311,12 +38311,12 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>AEL</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Anorthosis</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,7 +38430,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -38440,12 +38440,12 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Cinfães</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Alpendorada</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -38688,22 +38688,22 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Cinfães</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Alpendorada</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -38817,22 +38817,22 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Ittihad Tanger</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>FUS Rabat</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -38946,22 +38946,22 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -39204,22 +39204,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>AVS</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -39591,7 +39591,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Ittihad Tanger</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FUS Rabat</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Volos NFC</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39885,13 +39885,13 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N306" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -39924,10 +39924,10 @@
         <v>0</v>
       </c>
       <c r="Y306" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z306" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA306" t="n">
         <v>0</v>
@@ -39978,22 +39978,22 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -40107,22 +40107,22 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>AVS</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -40246,12 +40246,12 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -40623,7 +40623,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40659,13 +40659,13 @@
         </is>
       </c>
       <c r="L312" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N312" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O312" t="n">
         <v>0</v>
@@ -40752,22 +40752,22 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,22 +40881,22 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Cesena</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Győri ETO</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -41139,7 +41139,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -41149,12 +41149,12 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -41175,13 +41175,13 @@
         </is>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M316" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N316" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O316" t="n">
         <v>0</v>
@@ -41268,22 +41268,22 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -41397,22 +41397,22 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Győri ETO</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -41526,7 +41526,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -41536,12 +41536,12 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Cesena</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -41655,7 +41655,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -41665,12 +41665,12 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Saint-Étienne</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -41784,7 +41784,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -41794,12 +41794,12 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>APS Bomet</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -41913,7 +41913,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -41923,12 +41923,12 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -42042,7 +42042,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -42052,12 +42052,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -42171,7 +42171,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -42181,12 +42181,12 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>APS Bomet</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -42300,7 +42300,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -42310,12 +42310,12 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -42429,22 +42429,22 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -42465,13 +42465,13 @@
         </is>
       </c>
       <c r="L326" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N326" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O326" t="n">
         <v>0</v>
@@ -42558,7 +42558,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -42568,12 +42568,12 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -42594,13 +42594,13 @@
         </is>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="M327" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="N327" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O327" t="n">
         <v>0</v>
@@ -42639,10 +42639,10 @@
         <v>0</v>
       </c>
       <c r="AA327" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB327" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC327" t="n">
         <v>0</v>
@@ -42687,22 +42687,22 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -42723,13 +42723,13 @@
         </is>
       </c>
       <c r="L328" t="n">
-        <v>8.5</v>
+        <v>2.9</v>
       </c>
       <c r="M328" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="N328" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="O328" t="n">
         <v>0</v>
@@ -42768,10 +42768,10 @@
         <v>0</v>
       </c>
       <c r="AA328" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB328" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC328" t="n">
         <v>0</v>
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -43084,12 +43084,12 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Saint-Étienne</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -43203,7 +43203,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -43213,12 +43213,12 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -43332,7 +43332,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -43342,12 +43342,12 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -43848,7 +43848,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Slovakia Super Liga</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -43858,12 +43858,12 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Žilina</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>FK Košice</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -43977,22 +43977,22 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Slovakia Super Liga</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Žilina</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>FK Košice</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -44013,13 +44013,13 @@
         </is>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M338" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N338" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O338" t="n">
         <v>0</v>
@@ -44052,10 +44052,10 @@
         <v>0</v>
       </c>
       <c r="Y338" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z338" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA338" t="n">
         <v>0</v>
@@ -44106,22 +44106,22 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -44142,13 +44142,13 @@
         </is>
       </c>
       <c r="L339" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N339" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O339" t="n">
         <v>0</v>
@@ -44181,10 +44181,10 @@
         <v>0</v>
       </c>
       <c r="Y339" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z339" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA339" t="n">
         <v>0</v>
@@ -44493,7 +44493,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -44503,12 +44503,12 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>KCB</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Gor Mahia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -44529,13 +44529,13 @@
         </is>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M342" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N342" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O342" t="n">
         <v>0</v>
@@ -44568,16 +44568,16 @@
         <v>0</v>
       </c>
       <c r="Y342" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z342" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA342" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB342" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC342" t="n">
         <v>0</v>
@@ -44622,7 +44622,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -44632,12 +44632,12 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -44658,13 +44658,13 @@
         </is>
       </c>
       <c r="L343" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N343" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O343" t="n">
         <v>0</v>
@@ -44697,16 +44697,16 @@
         <v>0</v>
       </c>
       <c r="Y343" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z343" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA343" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB343" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC343" t="n">
         <v>0</v>
@@ -44751,7 +44751,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
@@ -44761,12 +44761,12 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -44890,12 +44890,12 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Zamora CF</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45009,22 +45009,22 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Zamora CF</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45138,22 +45138,22 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>KCB</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Gor Mahia</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -46299,7 +46299,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -46309,12 +46309,12 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46438,12 +46438,12 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46557,7 +46557,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -46567,12 +46567,12 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46696,12 +46696,12 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -47202,7 +47202,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -47212,12 +47212,12 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47341,12 +47341,12 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -47367,13 +47367,13 @@
         </is>
       </c>
       <c r="L364" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="M364" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N364" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="O364" t="n">
         <v>0</v>
@@ -47406,16 +47406,16 @@
         <v>0</v>
       </c>
       <c r="Y364" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z364" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA364" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB364" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC364" t="n">
         <v>0</v>
@@ -47470,12 +47470,12 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -47496,13 +47496,13 @@
         </is>
       </c>
       <c r="L365" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="M365" t="n">
         <v>3.8</v>
       </c>
       <c r="N365" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="O365" t="n">
         <v>0</v>
@@ -47535,10 +47535,10 @@
         <v>0</v>
       </c>
       <c r="Y365" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="Z365" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AA365" t="n">
         <v>0</v>
@@ -47589,7 +47589,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -47599,12 +47599,12 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47625,13 +47625,13 @@
         </is>
       </c>
       <c r="L366" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M366" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N366" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O366" t="n">
         <v>0</v>
@@ -47670,10 +47670,10 @@
         <v>0</v>
       </c>
       <c r="AA366" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB366" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC366" t="n">
         <v>0</v>
@@ -47718,7 +47718,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -47728,12 +47728,12 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -47754,13 +47754,13 @@
         </is>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M367" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N367" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O367" t="n">
         <v>0</v>
@@ -47793,10 +47793,10 @@
         <v>0</v>
       </c>
       <c r="Y367" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z367" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA367" t="n">
         <v>0</v>
@@ -47847,7 +47847,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -47857,12 +47857,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Monterey Bay</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -47986,12 +47986,12 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -48012,13 +48012,13 @@
         </is>
       </c>
       <c r="L369" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="M369" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="N369" t="n">
-        <v>3.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O369" t="n">
         <v>0</v>
@@ -48057,10 +48057,10 @@
         <v>0</v>
       </c>
       <c r="AA369" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB369" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC369" t="n">
         <v>0</v>
@@ -48105,7 +48105,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -48115,12 +48115,12 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -48244,12 +48244,12 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -48363,7 +48363,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -48373,12 +48373,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -48502,12 +48502,12 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Sporting KC</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -48528,13 +48528,13 @@
         </is>
       </c>
       <c r="L373" t="n">
-        <v>2.1</v>
+        <v>1.52</v>
       </c>
       <c r="M373" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N373" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="O373" t="n">
         <v>0</v>
@@ -48567,16 +48567,16 @@
         <v>0</v>
       </c>
       <c r="Y373" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z373" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AA373" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB373" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC373" t="n">
         <v>0</v>
@@ -48631,12 +48631,12 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Sporting KC</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -48657,13 +48657,13 @@
         </is>
       </c>
       <c r="L374" t="n">
-        <v>1.52</v>
+        <v>2.65</v>
       </c>
       <c r="M374" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="N374" t="n">
-        <v>6</v>
+        <v>2.27</v>
       </c>
       <c r="O374" t="n">
         <v>0</v>
@@ -48696,16 +48696,16 @@
         <v>0</v>
       </c>
       <c r="Y374" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z374" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA374" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB374" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC374" t="n">
         <v>0</v>
@@ -48889,12 +48889,12 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="G376" t="n">
@@ -48915,13 +48915,13 @@
         </is>
       </c>
       <c r="L376" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M376" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N376" t="n">
-        <v>2.27</v>
+        <v>3.05</v>
       </c>
       <c r="O376" t="n">
         <v>0</v>
@@ -48954,16 +48954,16 @@
         <v>0</v>
       </c>
       <c r="Y376" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z376" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA376" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB376" t="n">
         <v>1.6</v>
-      </c>
-      <c r="Z376" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA376" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB376" t="n">
-        <v>0</v>
       </c>
       <c r="AC376" t="n">
         <v>0</v>
@@ -49147,12 +49147,12 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -49266,7 +49266,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -49276,12 +49276,12 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -49395,7 +49395,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -49405,12 +49405,12 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="G380" t="n">
